--- a/output/price_match.xlsx
+++ b/output/price_match.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Matched" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DATA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,162 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>SupplierArticle</t>
+          <t>MatchStatus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>OriginalProductName</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CanonicalProductName</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>UnitCost</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RetailPrice</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>StockQty</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SourceUnit</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>PackQty</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>OriginalPrice</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ImportedAt</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>SourceFile</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SKU-APPLE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Shampoo SVO APPLE 1 L</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SVO shampoo apple 1 l</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SVO SHAMPOO APPLE 1 L</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-08-06T16:38:28.379912+00:00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>PRICE.xlsx</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SKU-APPLE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Shampoo SVO APPLE 1 L</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SVO shampoo apple 1 l</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SVO SHAMPOO APPLE 1 L</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-08-06T16:38:28.379912+00:00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>PRICE.xlsx</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>MATCH</t>
+          <t>ReviewReason</t>
         </is>
       </c>
     </row>
